--- a/TImeline Project Presensikita kel 6.xlsx
+++ b/TImeline Project Presensikita kel 6.xlsx
@@ -272,7 +272,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF165B47"/>
-        <bgColor rgb="FF2D5A4C"/>
+        <bgColor rgb="FF336B57"/>
       </patternFill>
     </fill>
     <fill>
@@ -312,7 +312,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -322,114 +322,105 @@
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left style="medium">
-        <color rgb="FF0F2820"/>
+        <color rgb="FF0F172A"/>
       </left>
       <right style="medium">
-        <color rgb="FF0F2820"/>
+        <color rgb="FF0F172A"/>
       </right>
       <top style="medium">
-        <color rgb="FF0F2820"/>
+        <color rgb="FF0F172A"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right style="medium">
-        <color rgb="FF0F2820"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
       <left style="medium">
-        <color rgb="FF0F2820"/>
+        <color rgb="FF0F172A"/>
       </left>
       <right style="medium">
-        <color rgb="FF334155"/>
+        <color rgb="FF0F172A"/>
       </right>
       <top style="thin">
-        <color rgb="FF2D5A4C"/>
+        <color rgb="FF336B57"/>
       </top>
       <bottom style="medium">
-        <color rgb="FF0F2820"/>
+        <color rgb="FF0F172A"/>
       </bottom>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
-        <color rgb="FF2D5A4C"/>
+        <color rgb="FF336B57"/>
       </left>
       <right style="thin">
-        <color rgb="FF2D5A4C"/>
+        <color rgb="FF336B57"/>
       </right>
       <top style="thin">
-        <color rgb="FF2D5A4C"/>
+        <color rgb="FF336B57"/>
       </top>
       <bottom style="medium">
-        <color rgb="FF0F2820"/>
+        <color rgb="FF0F172A"/>
       </bottom>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
-        <color rgb="FF2D5A4C"/>
+        <color rgb="FF336B57"/>
       </left>
       <right style="medium">
-        <color rgb="FF0F2820"/>
+        <color rgb="FF0F172A"/>
       </right>
       <top style="thin">
-        <color rgb="FF2D5A4C"/>
+        <color rgb="FF336B57"/>
       </top>
       <bottom style="medium">
-        <color rgb="FF0F2820"/>
+        <color rgb="FF0F172A"/>
       </bottom>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left style="medium">
-        <color rgb="FF0F2820"/>
+        <color rgb="FF0F172A"/>
       </left>
       <right style="medium">
-        <color rgb="FF334155"/>
+        <color rgb="FF0F172A"/>
       </right>
       <top/>
       <bottom style="medium">
-        <color rgb="FF475569"/>
+        <color rgb="FF0F172A"/>
       </bottom>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right style="thin">
-        <color rgb="FFE2E8F0"/>
+        <color rgb="FF94A3B8"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color rgb="FFE2E8F0"/>
+        <color rgb="FF94A3B8"/>
       </bottom>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right style="thin">
-        <color rgb="FFE2E8F0"/>
+        <color rgb="FF94A3B8"/>
       </right>
       <top/>
       <bottom style="medium">
-        <color rgb="FF475569"/>
+        <color rgb="FF0F172A"/>
       </bottom>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right style="medium">
-        <color rgb="FF0F2820"/>
+        <color rgb="FF0F172A"/>
       </right>
       <top/>
       <bottom style="medium">
-        <color rgb="FF475569"/>
+        <color rgb="FF0F172A"/>
       </bottom>
       <diagonal/>
     </border>
@@ -459,7 +450,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -468,28 +459,28 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="6" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -500,7 +491,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -512,7 +503,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -520,7 +511,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="8" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -528,15 +519,11 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="9" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="10" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="10" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="10" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -561,10 +548,10 @@
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800000"/>
       <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF0F172A"/>
+      <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF165B47"/>
+      <rgbColor rgb="FF336B57"/>
       <rgbColor rgb="FFC0C0C0"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
@@ -574,38 +561,38 @@
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFEDF2F7"/>
+      <rgbColor rgb="FFFAF5FF"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF2D5A4C"/>
+      <rgbColor rgb="FF165B47"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFF0F9FF"/>
-      <rgbColor rgb="FFE2E8F0"/>
+      <rgbColor rgb="FFEDF2F7"/>
       <rgbColor rgb="FFF8FAFC"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFAF5FF"/>
+      <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF475569"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF94A3B8"/>
+      <rgbColor rgb="FF0F172A"/>
+      <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF0F382C"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF0F2820"/>
       <rgbColor rgb="FF1E4035"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF334155"/>
+      <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF1E293B"/>
     </indexedColors>
   </colors>
@@ -874,300 +861,298 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J2" s="2"/>
-    </row>
+    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="3" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="9"/>
-      <c r="J4" s="10"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="9"/>
     </row>
     <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7"/>
-      <c r="B5" s="9" t="s">
+      <c r="A5" s="6"/>
+      <c r="B5" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="9"/>
-      <c r="J5" s="10"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9" t="s">
+      <c r="A6" s="6"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9" t="s">
+      <c r="D6" s="8"/>
+      <c r="E6" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9" t="s">
+      <c r="F6" s="8"/>
+      <c r="G6" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="10"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="9"/>
     </row>
     <row r="7" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="H7" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="I7" s="12"/>
-      <c r="J7" s="13"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="12"/>
     </row>
     <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7"/>
-      <c r="B8" s="11" t="s">
+      <c r="A8" s="6"/>
+      <c r="B8" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="H8" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="I8" s="12"/>
-      <c r="J8" s="13"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="12"/>
     </row>
     <row r="9" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7"/>
-      <c r="B9" s="12" t="s">
+      <c r="A9" s="6"/>
+      <c r="B9" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12" t="s">
+      <c r="C9" s="11"/>
+      <c r="D9" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12" t="s">
+      <c r="E9" s="11"/>
+      <c r="F9" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12" t="s">
+      <c r="G9" s="11"/>
+      <c r="H9" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="I9" s="12"/>
-      <c r="J9" s="13"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="12"/>
     </row>
     <row r="10" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="15"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="14"/>
     </row>
     <row r="11" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="15"/>
+      <c r="A11" s="6"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="14"/>
     </row>
     <row r="12" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="15"/>
+      <c r="A12" s="6"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="14"/>
     </row>
     <row r="13" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="17"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="16"/>
     </row>
     <row r="14" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="17"/>
+      <c r="A14" s="6"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="16"/>
     </row>
     <row r="15" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="17"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="16"/>
     </row>
     <row r="16" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="18"/>
-      <c r="J16" s="19"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="18"/>
     </row>
     <row r="17" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="19"/>
+      <c r="A17" s="6"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="18"/>
     </row>
     <row r="18" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="19"/>
+      <c r="A18" s="6"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="17"/>
+      <c r="J18" s="18"/>
     </row>
     <row r="19" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
